--- a/docs/AI_scientist_审题人登记表.xlsx
+++ b/docs/AI_scientist_审题人登记表.xlsx
@@ -8,10 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Pro_moonshotai_Kimi-K2.5_no" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Pro_zai-org_GLM-5_no-review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Qwen_Qwen3.5-397B-A17B_no-r" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Qwen_Qwen3.5-397B-A17B_no_1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_deepseek-ai_DeepSeek-V3.2_n" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Pro_moonshotai_Kimi-K2.5__1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Pro_moonshotai_Kimi-K2.5__2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Pro_zai-org_GLM-5_no-review" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Pro_zai-org_GLM-5_no-revi_1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Pro_zai-org_GLM-5_no-revi_2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Qwen_Qwen3.5-397B-A17B_no-r" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Qwen_Qwen3.5-397B-A17B_no_1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_Qwen_Qwen3.5-397B-A17B_no_2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_deepseek-ai_DeepSeek-V3.2_n" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_deepseek-ai_DeepSeek-V3.2_1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="new_deepseek-ai_DeepSeek-V3.2_2" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,13 +60,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -427,19 +437,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,87 +462,154 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>字段 \ 场景</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>scenario_id（场景）</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>审题人</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>领题时间</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提交审查时间</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>01a_SymbolicPatternReasoning_BenchmarkSelection</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>02a_SymbolicPatternReasoning_LabelNoiseCeiling</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>03a_RecommendationSystem_RecSysV2LaunchEvaluation</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>04a_RareEvent_ClassificationKPI</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>05a_SocialScience_InterviewThematicAnalysis</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>06a_RetailAnalytics_AdSpendStoreSales</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>07a_Research_CatalystX9_LabNotebookSOP</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>08a_StructuralHealth_SensorVibrationPanel</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>09a_NuclearScience_Iodine131DecayAnalysis</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>审题人</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>领题时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>提交审查时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>负责人确认时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10a_Archaeology_RadiocarbonSiteChronology</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11a_DataScience_TelemetryExportMergeReport</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>状态说明：已领 / 已审 / 负责人已确认</t>
         </is>
@@ -543,8 +617,387 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次 run_id（完整）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>new_deepseek-ai_DeepSeek-V3.2_no-reviewer_20260407_211506</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>scenario_id（场景）</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>审题人</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>领题时间</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提交审查时间</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01a_SymbolicPatternReasoning_BenchmarkSelection</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>02a_SymbolicPatternReasoning_LabelNoiseCeiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>03a_RecommendationSystem_RecSysV2LaunchEvaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04a_RareEvent_ClassificationKPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05a_SocialScience_InterviewThematicAnalysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06a_RetailAnalytics_AdSpendStoreSales</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07a_Research_CatalystX9_LabNotebookSOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08a_StructuralHealth_SensorVibrationPanel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>09a_NuclearScience_Iodine131DecayAnalysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10a_Archaeology_RadiocarbonSiteChronology</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11a_DataScience_TelemetryExportMergeReport</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>状态说明：已领 / 已审 / 负责人已确认</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次 run_id（完整）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>new_deepseek-ai_DeepSeek-V3.2_no-reviewer_20260408_002436</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>scenario_id（场景）</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>审题人</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>领题时间</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提交审查时间</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01b_ComputationalLinguistics_MorphologicalSegmentationSuite</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>状态说明：已领 / 已审 / 负责人已确认</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次 run_id（完整）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>new_deepseek-ai_DeepSeek-V3.2_no-reviewer_20260408_002437</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>scenario_id（场景）</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>审题人</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>领题时间</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提交审查时间</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01c_BiomedicalImaging_CellBenchmarkPicker</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>状态说明：已领 / 已审 / 负责人已确认</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -556,15 +1009,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,72 +1029,159 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>new_Pro_zai-org_GLM-5_no-reviewer_20260407_211651</t>
+          <t>new_Pro_moonshotai_Kimi-K2.5_no-reviewer_20260407_222651</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>字段 \ 场景</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>01a_SymbolicPatternReasoning_BenchmarkSelection</t>
+          <t>scenario_id（场景）</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>02a_SymbolicPatternReasoning_LabelNoiseCeiling</t>
+          <t>审题人</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>03a_RecommendationSystem_RecSysV2LaunchEvaluation</t>
+          <t>领题时间</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>04a_RareEvent_ClassificationKPI</t>
+          <t>提交审查时间</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>05a_SocialScience_InterviewThematicAnalysis</t>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>审题人</t>
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01b_ComputationalLinguistics_MorphologicalSegmentationSuite</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>领题时间</t>
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>02b_FinancialML_CreditDefaultSPR</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>提交审查时间</t>
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>03b_HealthInformatics_EDTriageModelLaunch</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>负责人确认时间</t>
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04b_ControlSystems_LQRGainSchedule</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05b_Genomics_VariantCallingPipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06b_PublicHealth_AirPollutionClinicPanel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07b_MaterialsScience_NanoparticleSynthSOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08b_EnergySystems_LoadForecastCSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>09b_EverydayScience_BeverageCooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10b_Geophysics_MicroseismicBrief</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11b_Logistics_MultiWMSInventoryRecon</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>状态说明：已领 / 已审 / 负责人已确认</t>
         </is>
@@ -648,8 +1189,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -661,21 +1202,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -686,102 +1222,59 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>new_Qwen_Qwen3.5-397B-A17B_no-reviewer_20260407_211635</t>
+          <t>new_Pro_moonshotai_Kimi-K2.5_no-reviewer_20260407_231905</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>字段 \ 场景</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>01a_SymbolicPatternReasoning_BenchmarkSelection</t>
+          <t>scenario_id（场景）</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>02a_SymbolicPatternReasoning_LabelNoiseCeiling</t>
+          <t>审题人</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>03a_RecommendationSystem_RecSysV2LaunchEvaluation</t>
+          <t>领题时间</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>04a_RareEvent_ClassificationKPI</t>
+          <t>提交审查时间</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>05a_SocialScience_InterviewThematicAnalysis</t>
+          <t>负责人确认时间</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>06a_RetailAnalytics_AdSpendStoreSales</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>07a_Research_CatalystX9_LabNotebookSOP</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>08a_StructuralHealth_SensorVibrationPanel</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>09a_NuclearScience_Iodine131DecayAnalysis</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>10a_Archaeology_RadiocarbonSiteChronology</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>11a_DataScience_TelemetryExportMergeReport</t>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>审题人</t>
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01c_BiomedicalImaging_CellBenchmarkPicker</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>领题时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>提交审查时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>负责人确认时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>状态说明：已领 / 已审 / 负责人已确认</t>
         </is>
@@ -789,8 +1282,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -802,15 +1295,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -821,72 +1315,159 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>new_Qwen_Qwen3.5-397B-A17B_no-reviewer_20260407_215657</t>
+          <t>new_Pro_zai-org_GLM-5_no-reviewer_20260407_211651</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>字段 \ 场景</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>01b_ComputationalLinguistics_MorphologicalSegmentationSuite</t>
+          <t>scenario_id（场景）</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>02b_FinancialML_CreditDefaultSPR</t>
+          <t>审题人</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>03b_HealthInformatics_EDTriageModelLaunch</t>
+          <t>领题时间</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>04b_ControlSystems_LQRGainSchedule</t>
+          <t>提交审查时间</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>05b_Genomics_VariantCallingPipeline</t>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>审题人</t>
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01a_SymbolicPatternReasoning_BenchmarkSelection</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>领题时间</t>
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>02a_SymbolicPatternReasoning_LabelNoiseCeiling</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>提交审查时间</t>
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>03a_RecommendationSystem_RecSysV2LaunchEvaluation</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>负责人确认时间</t>
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04a_RareEvent_ClassificationKPI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05a_SocialScience_InterviewThematicAnalysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06a_RetailAnalytics_AdSpendStoreSales</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07a_Research_CatalystX9_LabNotebookSOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08a_StructuralHealth_SensorVibrationPanel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>09a_NuclearScience_Iodine131DecayAnalysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10a_Archaeology_RadiocarbonSiteChronology</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11a_DataScience_TelemetryExportMergeReport</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>状态说明：已领 / 已审 / 负责人已确认</t>
         </is>
@@ -894,8 +1475,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -907,11 +1488,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -922,52 +1508,59 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>new_deepseek-ai_DeepSeek-V3.2_no-reviewer_20260407_211506</t>
+          <t>new_Pro_zai-org_GLM-5_no-reviewer_20260407_225140</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>字段 \ 场景</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>01a_SymbolicPatternReasoning_BenchmarkSelection</t>
+          <t>scenario_id（场景）</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>审题人</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>领题时间</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提交审查时间</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>审题人</t>
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01b_ComputationalLinguistics_MorphologicalSegmentationSuite</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>领题时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>提交审查时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>负责人确认时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>状态说明：已领 / 已审 / 负责人已确认</t>
         </is>
@@ -975,8 +1568,680 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1"/>
-    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次 run_id（完整）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>new_Pro_zai-org_GLM-5_no-reviewer_20260407_225141</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>scenario_id（场景）</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>审题人</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>领题时间</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提交审查时间</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01c_BiomedicalImaging_CellBenchmarkPicker</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>状态说明：已领 / 已审 / 负责人已确认</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次 run_id（完整）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>new_Qwen_Qwen3.5-397B-A17B_no-reviewer_20260407_211635</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>scenario_id（场景）</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>审题人</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>领题时间</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提交审查时间</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01a_SymbolicPatternReasoning_BenchmarkSelection</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>02a_SymbolicPatternReasoning_LabelNoiseCeiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>03a_RecommendationSystem_RecSysV2LaunchEvaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04a_RareEvent_ClassificationKPI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05a_SocialScience_InterviewThematicAnalysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06a_RetailAnalytics_AdSpendStoreSales</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07a_Research_CatalystX9_LabNotebookSOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08a_StructuralHealth_SensorVibrationPanel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>09a_NuclearScience_Iodine131DecayAnalysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10a_Archaeology_RadiocarbonSiteChronology</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11a_DataScience_TelemetryExportMergeReport</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>状态说明：已领 / 已审 / 负责人已确认</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次 run_id（完整）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>new_Qwen_Qwen3.5-397B-A17B_no-reviewer_20260407_215657</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>scenario_id（场景）</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>审题人</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>领题时间</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提交审查时间</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01b_ComputationalLinguistics_MorphologicalSegmentationSuite</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>02b_FinancialML_CreditDefaultSPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>03b_HealthInformatics_EDTriageModelLaunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04b_ControlSystems_LQRGainSchedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05b_Genomics_VariantCallingPipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06b_PublicHealth_AirPollutionClinicPanel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07b_MaterialsScience_NanoparticleSynthSOP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08b_EnergySystems_LoadForecastCSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>09b_EverydayScience_BeverageCooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10b_Geophysics_MicroseismicBrief</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11b_Logistics_MultiWMSInventoryRecon</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>状态说明：已领 / 已审 / 负责人已确认</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次 run_id（完整）</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>new_Qwen_Qwen3.5-397B-A17B_no-reviewer_20260407_222631</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>scenario_id（场景）</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>审题人</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>领题时间</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>提交审查时间</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>负责人确认时间</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01c_BiomedicalImaging_CellBenchmarkPicker</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>02c_AstroML_VariableStarClassification</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>03c_RLPolicy_RobotPickPlaceComparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04c_NumericalPDE_PorousMediumTravelingWave</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05c_CyberSecurity_IncidentNarrativeTriage</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06c_AgEcon_IrrigationYieldPanel</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07c_ClinicalOps_ColdChainShipmentProtocol</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08c_Oceanography_CTDCruiseStations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>09c_Ecology_SpeciesAreaIsland</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10c_Econometrics_REITInflationPanel</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11c_DigitalHumanities_MuseumProvenanceMerge</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>状态说明：已领 / 已审 / 负责人已确认</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="B1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
